--- a/AAII_Financials/Yearly/EL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/EL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
   <si>
     <t>EL</t>
   </si>
@@ -656,220 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44012</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43646</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43281</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42916</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42551</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42185</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41820</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41455</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>41090</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>15049000</v>
+      </c>
+      <c r="E8" s="3">
         <v>14326000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15608000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>15910000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>17737000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>16215000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>14294000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>14863000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13683000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>11824000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11262300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10780400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10968900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10183200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9713600</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3730000</v>
+        <v>3689000</v>
       </c>
       <c r="E9" s="3">
-        <v>4423000</v>
+        <v>3720000</v>
       </c>
       <c r="F9" s="3">
+        <v>4424000</v>
+      </c>
+      <c r="G9" s="3">
         <v>4561000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4300000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3832000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3552000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3365000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2826000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2437000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2181100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2100600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2158100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2024700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1994300</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>10596000</v>
+        <v>11360000</v>
       </c>
       <c r="E10" s="3">
-        <v>11185000</v>
+        <v>10606000</v>
       </c>
       <c r="F10" s="3">
+        <v>11184000</v>
+      </c>
+      <c r="G10" s="3">
         <v>11349000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>13437000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>12383000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>10742000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>11498000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10857000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9387000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>9081200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8679800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8810800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>8158500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>7719300</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -888,46 +900,47 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>278000</v>
+      </c>
+      <c r="E12" s="3">
         <v>316000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>360000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>344000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>307000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>243000</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>202000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>181000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>179000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>191300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>178100</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>8</v>
@@ -935,9 +948,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,87 +999,93 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1928000</v>
+        <v>898000</v>
       </c>
       <c r="E14" s="3">
-        <v>595000</v>
+        <v>1938000</v>
       </c>
       <c r="F14" s="3">
+        <v>594000</v>
+      </c>
+      <c r="G14" s="3">
         <v>265000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>383000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-444000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>965000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>297000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>206000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>226000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>133100</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-2800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>54600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>82800</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>796000</v>
+      </c>
+      <c r="E15" s="3">
         <v>829000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>825000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>744000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>727000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>651000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>611000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>557000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>531000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1079,9 +1101,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,104 +1122,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>13195000</v>
+        <v>13390000</v>
       </c>
       <c r="E17" s="3">
-        <v>14030000</v>
+        <v>13185000</v>
       </c>
       <c r="F17" s="3">
+        <v>14031000</v>
+      </c>
+      <c r="G17" s="3">
         <v>14124000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14182000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13205000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12193000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12261000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11425000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10132000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9652000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9174100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9141300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8676300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8401900</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1131000</v>
+        <v>1659000</v>
       </c>
       <c r="E18" s="3">
-        <v>1578000</v>
+        <v>1141000</v>
       </c>
       <c r="F18" s="3">
+        <v>1577000</v>
+      </c>
+      <c r="G18" s="3">
         <v>1786000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3555000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3010000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2101000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2602000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2258000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1692000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1610300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1606300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1827600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1506900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1311700</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1213,8 +1245,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1227,234 +1260,249 @@
       <c r="F20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3">
         <v>-1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-23000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-77000</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>28000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>15600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>14300</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>23100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>10500</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1960000</v>
+        <v>2455000</v>
       </c>
       <c r="E21" s="3">
-        <v>2403000</v>
+        <v>1970000</v>
       </c>
       <c r="F21" s="3">
+        <v>2402000</v>
+      </c>
+      <c r="G21" s="3">
         <v>2530000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4283000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3660000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2735000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3236000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2789000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2184000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2040600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2029900</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3">
         <v>1618000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>334000</v>
+      </c>
+      <c r="E22" s="3">
         <v>357000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>378000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>255000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>167000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>173000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>161000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>133000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>128000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>103000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>70700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>60000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>50800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>54800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>61100</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>517000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1040000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>772000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1397000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3036000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3331000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1046000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2307000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1980000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1617000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1555200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1560600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1776800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1475200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1261100</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>335000</v>
+      </c>
+      <c r="E24" s="3">
         <v>93000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>363000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>387000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>628000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>456000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>350000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>513000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>863000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>361000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>434400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>467200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>567700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>451400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>400600</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1500,105 +1548,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1133000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>409000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1010000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2408000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2875000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>696000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1794000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1117000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1256000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1120800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1093400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1209100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1023800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>860500</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1133000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>390000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1006000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2390000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2870000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>684000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1785000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1108000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1249000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1114600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1088900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1204100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1019800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>856900</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1644,9 +1701,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1674,8 +1734,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -1692,9 +1752,12 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1740,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,9 +1854,12 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1803,90 +1872,96 @@
       <c r="F32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3">
         <v>1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>23000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>77000</v>
       </c>
-      <c r="K32" s="3" t="s">
+      <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-28000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-15600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-14300</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-23100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-10500</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1133000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>390000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1006000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2390000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2870000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>684000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1785000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1108000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1249000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1114600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1088900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1204100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1019800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>856900</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1932,110 +2007,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1133000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>390000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1006000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2390000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2870000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>684000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1785000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1108000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1249000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1114600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1088900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1204100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1019800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>856900</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44012</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43646</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43281</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42916</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42551</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42185</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41820</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41455</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>41090</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2054,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2074,56 +2159,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3498000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2921000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3395000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4029000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3957000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4958000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5022000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2987000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2181000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1136000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>914100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1021400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1629100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1495700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1347700</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2137,233 +2226,248 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>24000</v>
-      </c>
-      <c r="H42" s="3">
-        <v>15000</v>
       </c>
       <c r="I42" s="3">
         <v>15000</v>
       </c>
       <c r="J42" s="3">
+        <v>15000</v>
+      </c>
+      <c r="K42" s="3">
         <v>3000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>534000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>605000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>469300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>503700</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>8</v>
+      <c r="P42" s="3">
+        <v>0</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1518000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1530000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1727000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1452000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1629000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1702000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1194000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1831000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1487000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1395000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1258300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1174500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1379300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1171700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1060300</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1999000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2074000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2175000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2979000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2920000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2505000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2062000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2006000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1618000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1479000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1263400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1215800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1294000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1113900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>983600</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E45" s="3">
         <v>42000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>76000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>20000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>191000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>52000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>87000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>27000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>33000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>349000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>320000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>268200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>522800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>515900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>927000</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7612000</v>
+      </c>
+      <c r="E46" s="3">
         <v>7069000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7922000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9139000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9298000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9768000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8892000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7212000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6168000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4964000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4225100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4183600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4825200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4297200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3855100</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2388,126 +2492,135 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3">
         <v>843000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1026000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1107700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>420300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>13600</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4545000</v>
+      </c>
+      <c r="E48" s="3">
         <v>5124000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4969000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4976000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4599000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4470000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4337000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2068000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1823000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1671000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1583300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1490200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1502600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1350700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1246400</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5686000</v>
+      </c>
+      <c r="E49" s="3">
         <v>5894000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7326000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8088000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5949000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6711000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3739000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3071000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3202000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3243000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1572300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1471400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1050500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1051100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>880800</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2553,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2601,57 +2717,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>492000</v>
+      </c>
+      <c r="E52" s="3">
         <v>466000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>442000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>352000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>369000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>391000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>769000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>510000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>411000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>664000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>734900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>661400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>476900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>446200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>433400</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2697,57 +2819,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19762000</v>
+      </c>
+      <c r="E54" s="3">
         <v>19892000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>21677000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>23415000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>20910000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21971000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17781000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13156000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12567000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11568000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9223300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8226900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7868800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7145200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6593000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2766,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2786,296 +2915,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1578000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1497000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1440000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1670000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1822000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1692000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1177000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1490000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1182000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>835000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>716700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>635400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>524500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>481700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>493800</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>902000</v>
+      </c>
+      <c r="E58" s="3">
         <v>409000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>858000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1354000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>633000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>411000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1600000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>542000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>209000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>189000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>331500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>29800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>18400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>18300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>219000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1018000</v>
+      </c>
+      <c r="E59" s="3">
         <v>875000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>748000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>545000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>312000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>747000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>514000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>320000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>46000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1799000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1632300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1561500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1532900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1434600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2728800</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6231000</v>
+      </c>
+      <c r="E60" s="3">
         <v>5435000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5702000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6240000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5815000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5298000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5179000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4605000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3310000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2823000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2680500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2129800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2056700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1934600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2125800</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8344000</v>
+      </c>
+      <c r="E61" s="3">
         <v>9058000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8968000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8815000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7012000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7688000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7192000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2896000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3361000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3383000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1910000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1595100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1324700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1326000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1069100</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>471000</v>
+      </c>
+      <c r="E62" s="3">
         <v>540000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>602000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>679000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>602000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>756000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>609000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>826000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>811000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>960000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1045500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>847700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>618000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>582700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>650600</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3121,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3169,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3217,57 +3371,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15956000</v>
+      </c>
+      <c r="E66" s="3">
         <v>16027000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16363000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16998000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14478000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>15023000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13819000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8745000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7857000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7184000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5651400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4583700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4013900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3858300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3859800</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3286,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3333,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3381,9 +3545,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3429,9 +3596,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3477,57 +3647,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>11341000</v>
+      </c>
+      <c r="E72" s="3">
         <v>11672000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>13427000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>13991000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>13912000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>12244000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>10134000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9984000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9040000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8452000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7693300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7004100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6265800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5364100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>4764900</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3573,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3621,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3669,57 +3851,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3806000</v>
+      </c>
+      <c r="E76" s="3">
         <v>3865000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5314000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5585000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5590000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6057000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3935000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4386000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4688000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4384000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3571900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3643200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3854900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3286900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2733200</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3765,110 +3953,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44012</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43646</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43281</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42916</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42551</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42185</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41820</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41455</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>41090</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1133000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>390000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1006000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2390000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2870000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>684000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1785000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1108000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1249000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1114600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1088900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1204100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1019800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>856900</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3887,56 +4084,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>691000</v>
+      </c>
+      <c r="E83" s="3">
         <v>698000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>681000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>599000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>567000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>541000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>538000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>506000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>480000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>464000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>414700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>409300</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R83" s="3">
         <v>295800</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3982,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4030,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4078,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4126,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,57 +4387,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1773000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1272000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2360000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1731000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3040000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3631000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2280000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2517000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2562000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1800000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1788700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1943300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1535200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1226300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1126700</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4243,56 +4462,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-457000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-602000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-919000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1003000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1040000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-637000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-623000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-744000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-629000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-504000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-525300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-473000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-510200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-461000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-420700</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4338,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4386,57 +4612,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-489000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-623000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-960000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3217000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-945000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1864000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1698000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>473000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-358000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2214000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1269300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1616200</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R94" s="3">
         <v>-428300</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4455,56 +4687,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>508000</v>
+      </c>
+      <c r="E96" s="3">
         <v>618000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>947000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>925000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>840000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>753000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>503000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>609000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>546000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-486000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-422500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-349900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-301800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-419200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-204000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4550,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4598,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4646,151 +4888,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-712000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1144000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2035000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1590000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3036000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1892000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1461000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2173000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1172000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>630000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-604900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-894800</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R100" s="3">
         <v>-585100</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E101" s="3">
         <v>21000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-32000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-60000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>61000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-8000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-11000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>13000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>6000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-21800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-40000</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R101" s="3">
         <v>-18600</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>577000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-474000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-634000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>72000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1001000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-64000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2035000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>806000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1045000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>222000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-107300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-607700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>133400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>148000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>94700</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
